--- a/data/preprocessed/classifications.xlsx
+++ b/data/preprocessed/classifications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N608"/>
+  <dimension ref="A1:N611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36444,6 +36444,202 @@
         <v>28.827035</v>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>node/12758714624</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Gamarjoba</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>restaurant; bar_with_food</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Caucasus</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Georgian</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>soup; salad; dessert; grill</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>The venue serves Georgian cuisine with dishes including khinkali, khachapuri, grilled mtsvadi, soup, salad, and dessert. The menu and listings explicitly identify the cuisine as Georgian and Caucasian.</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>official_menu (https://gamarjoba.us/menu/); reputable_listing (https://restaurantguru.com/Gamarjoba-Modern-Georgian-Bar-Chisinau); delivery_platform (https://foodhouse.md/en/gamarjoba); reputable_listing (https://g0.md/en/explore/gamarjoba-modern-georgian-bar)</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>food_specialty=khinkali; food_specialty=khachapuri; food_specialty=grilled_mtsvadi</t>
+        </is>
+      </c>
+      <c r="M609" t="n">
+        <v>47.040156</v>
+      </c>
+      <c r="N609" t="n">
+        <v>28.892219</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>node/12793508256</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Asti Restobar</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>restaurant; pub_with_food</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Eastern Europe</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Moldovan</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>soup</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>Multiple sources confirm the venue offers a menu with traditional dishes including soup and aperitifs, and is described as a culinary gem in Chisinau, Moldova. One listing refers to 'traditional grandma's soup', suggesting Moldovan regional cuisine. No explicit mention of Italian dishes or other cuisines. The name 'Asti' may suggest Italian influence but is not confirmed by menu or cuisine evidence.</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>reputable_listing (https://www.tripadvisor.com/Restaurant_Review-g294456-d33029121-Reviews-Asti_Restobar-Chisinau_Chisinau_District.html); reputable_listing (https://wanderlog.com/place/details/13914726/asti-restobar); official_menu (https://restaurantguru.com/Asti-Restobar-Chisinau/menu); reputable_listing (https://www.tripadvisor.com/Restaurants-g294456-c26-zfp3-Chisinau_Chisinau_District.html); osm</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>food_specialty=apertifs</t>
+        </is>
+      </c>
+      <c r="M610" t="n">
+        <v>47.006629</v>
+      </c>
+      <c r="N610" t="n">
+        <v>28.859486</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>node/13555963043</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Gastronomia Bistro</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>cafe_with_food</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr"/>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>dessert</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>The venue offers oysters, tuna tartare, and tiramisu, indicating a mix of savory and dessert items. No explicit mention of specific cuisines or nationalities in the menu or reviews.</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>reputable_listing (https://www.tripadvisor.com/Restaurant_Review-g294456-d7196258-Reviews-Gastrobar-Chisinau_Chisinau_District.html); reputable_listing (https://www.tripadvisor.com/Restaurants-g294456-Chisinau_Chisinau_District.html); reputable_listing (https://restaurantguru.com/Bistro-Chiparus-Chisinau); reputable_listing (https://restaurantguru.com/cafe-bistro-Chisinau); osm</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>food_specialty=tartare; food_specialty=oysters; food_specialty=tiramisu; establishment_concept=bistro</t>
+        </is>
+      </c>
+      <c r="M611" t="n">
+        <v>47.058183</v>
+      </c>
+      <c r="N611" t="n">
+        <v>28.890787</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/preprocessed/classifications.xlsx
+++ b/data/preprocessed/classifications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N611"/>
+  <dimension ref="A1:N612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36640,6 +36640,66 @@
         <v>28.890787</v>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>node/13569632069</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Augusto</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>cafe_with_food; pizzeria</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr"/>
+      <c r="H612" t="inlineStr"/>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>pizza; noodles; chicken; breakfast</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>The venue offers pizza, soba noodles, chicken, and breakfast items, indicating a full meal service with multiple savory specialties. The name and social media suggest a pizzeria and cafe, but no explicit cuisine claims are made in the evidence. No clear regional or national cuisine is identified.</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>official_social (https://www.instagram.com/augustopatiserie/); reputable_listing (https://ru.restaurantguru.com/Augusto-Chisinau); delivery_platform (https://glovoapp.com/md/en/chisinau/augusto-ksn/); official_menu (https://straus.md/restaurant/augusto-unotoro); official_social (https://www.facebook.com/augusto.pizzeria.cafe/)</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>food_specialty=beef</t>
+        </is>
+      </c>
+      <c r="M612" t="n">
+        <v>47.057786</v>
+      </c>
+      <c r="N612" t="n">
+        <v>28.890726</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
